--- a/artfynd/A 34015-2025 artfynd.xlsx
+++ b/artfynd/A 34015-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1641,6 +1641,218 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127414963</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92652</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Byssträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>691515</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7138689</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127414964</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Byssträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>691616</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7138989</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34015-2025 artfynd.xlsx
+++ b/artfynd/A 34015-2025 artfynd.xlsx
@@ -1647,7 +1647,7 @@
         <v>127414963</v>
       </c>
       <c r="B11" t="n">
-        <v>92652</v>
+        <v>92656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>127414964</v>
       </c>
       <c r="B12" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34015-2025 artfynd.xlsx
+++ b/artfynd/A 34015-2025 artfynd.xlsx
@@ -1647,7 +1647,7 @@
         <v>127414963</v>
       </c>
       <c r="B11" t="n">
-        <v>92656</v>
+        <v>92658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>127414964</v>
       </c>
       <c r="B12" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34015-2025 artfynd.xlsx
+++ b/artfynd/A 34015-2025 artfynd.xlsx
@@ -1647,7 +1647,7 @@
         <v>127414963</v>
       </c>
       <c r="B11" t="n">
-        <v>92658</v>
+        <v>92664</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34015-2025 artfynd.xlsx
+++ b/artfynd/A 34015-2025 artfynd.xlsx
@@ -1647,7 +1647,7 @@
         <v>127414963</v>
       </c>
       <c r="B11" t="n">
-        <v>92664</v>
+        <v>92667</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>127414964</v>
       </c>
       <c r="B12" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34015-2025 artfynd.xlsx
+++ b/artfynd/A 34015-2025 artfynd.xlsx
@@ -1647,7 +1647,7 @@
         <v>127414963</v>
       </c>
       <c r="B11" t="n">
-        <v>92667</v>
+        <v>92675</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>127414964</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34015-2025 artfynd.xlsx
+++ b/artfynd/A 34015-2025 artfynd.xlsx
@@ -1647,7 +1647,7 @@
         <v>127414963</v>
       </c>
       <c r="B11" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34015-2025 artfynd.xlsx
+++ b/artfynd/A 34015-2025 artfynd.xlsx
@@ -1647,7 +1647,7 @@
         <v>127414963</v>
       </c>
       <c r="B11" t="n">
-        <v>92676</v>
+        <v>92677</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34015-2025 artfynd.xlsx
+++ b/artfynd/A 34015-2025 artfynd.xlsx
@@ -1647,7 +1647,7 @@
         <v>127414963</v>
       </c>
       <c r="B11" t="n">
-        <v>92677</v>
+        <v>92678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34015-2025 artfynd.xlsx
+++ b/artfynd/A 34015-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283168</v>
+        <v>121283169</v>
       </c>
       <c r="B2" t="n">
-        <v>74720</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691486</v>
+        <v>691491</v>
       </c>
       <c r="R2" t="n">
-        <v>7139093</v>
+        <v>7139117</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283162</v>
+        <v>121283158</v>
       </c>
       <c r="B3" t="n">
-        <v>91627</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691449</v>
+        <v>691494</v>
       </c>
       <c r="R3" t="n">
-        <v>7138784</v>
+        <v>7138800</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283173</v>
+        <v>121283162</v>
       </c>
       <c r="B4" t="n">
-        <v>78614</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691493</v>
+        <v>691449</v>
       </c>
       <c r="R4" t="n">
-        <v>7139116</v>
+        <v>7138784</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121283158</v>
+        <v>127414963</v>
       </c>
       <c r="B5" t="n">
-        <v>91627</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,34 +990,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Byssträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691494</v>
+        <v>691515</v>
       </c>
       <c r="R5" t="n">
-        <v>7138800</v>
+        <v>7138689</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1048,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,53 +1073,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121283169</v>
+        <v>121283160</v>
       </c>
       <c r="B6" t="n">
-        <v>82398</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691491</v>
+        <v>691460</v>
       </c>
       <c r="R6" t="n">
-        <v>7139117</v>
+        <v>7138784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1164,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1206,37 +1186,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121283164</v>
+        <v>121283173</v>
       </c>
       <c r="B7" t="n">
-        <v>97064</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691467</v>
+        <v>691493</v>
       </c>
       <c r="R7" t="n">
-        <v>7139055</v>
+        <v>7139116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121283166</v>
+        <v>121283168</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,42 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Byssträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691511</v>
+        <v>691486</v>
       </c>
       <c r="R8" t="n">
-        <v>7139141</v>
+        <v>7139093</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,15 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121283160</v>
+        <v>127414964</v>
       </c>
       <c r="B9" t="n">
-        <v>78614</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1442,34 +1399,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Byssträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691460</v>
+        <v>691616</v>
       </c>
       <c r="R9" t="n">
-        <v>7138784</v>
+        <v>7138989</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,12 +1457,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,48 +1482,39 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121378240</v>
+        <v>121283166</v>
       </c>
       <c r="B10" t="n">
-        <v>56339</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208260</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1566,25 +1523,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hundliden, Ly lm</t>
+          <t>Byssträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691402</v>
+        <v>691511</v>
       </c>
       <c r="R10" t="n">
-        <v>7138974</v>
+        <v>7139141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,68 +1581,76 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127414963</v>
+        <v>121378240</v>
       </c>
       <c r="B11" t="n">
-        <v>92678</v>
+        <v>56905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>208260</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Byssträsk, Ly lm</t>
+          <t>Hundliden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691515</v>
+        <v>691402</v>
       </c>
       <c r="R11" t="n">
-        <v>7138689</v>
+        <v>7138974</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,17 +1677,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,67 +1691,64 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127414964</v>
+        <v>121283164</v>
       </c>
       <c r="B12" t="n">
-        <v>78787</v>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Byssträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691616</v>
+        <v>691467</v>
       </c>
       <c r="R12" t="n">
-        <v>7138989</v>
+        <v>7139055</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,17 +1775,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1844,15 +1795,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34015-2025 artfynd.xlsx
+++ b/artfynd/A 34015-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121283169</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121283158</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121283162</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414963</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121283160</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121283173</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121283168</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414964</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121283166</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121378240</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,8 +1863,26 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121283164</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>